--- a/extenbooks/S401_extenbook.xlsx
+++ b/extenbooks/S401_extenbook.xlsx
@@ -4285,7 +4285,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5584,11 +5584,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5611,76 +5611,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Derived numerical illustration of Fig 4.16 (per-worker wage cost curves). XR-axi</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S401_research.json", "adequacy_report": "Technical/docs/chapters/CH4_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S401_DPR.md", "epr": "Technical/docs/series/S401_EPR.md", "loader": "Technical/code/L01_loaders/L01_S401_load.py", "processor": "Technical/code/P02_processors/P02_S401_construct.py", "validator": "Technical/code/V03_validators/V03_S401_validate.py", "processed": "Technical/data/processed/S401.parquet", "chopped_csv": "Technical/chopped/S401.csv", "extenbook_xlsx": "Technical/extenbooks/S401_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T21:57:52.480731+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S401_extenbook.xlsx
+++ b/extenbooks/S401_extenbook.xlsx
@@ -4232,7 +4232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A146"/>
+  <dimension ref="A1:A145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4264,14 +4264,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record (DPR)** — the internal, full-provenance companion to the public Explainer.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record (source-and-construction detail)</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S401_research.json`</t>
+          <t>- Series research notes: `Technical/research/S401_research.json`</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S401-A** | XR rows 0–20 (21 points, indexed by row, not year) | Shaikh, *Capitalism* (2016), Appendix 4.2 Table 4.2.4, per-worker-wage columns | money units per unit of output | Reconstructed CSV `SalvagedInputs/book_data/Reconstructed/Appendix_4_2_Table4.csv`, columns `XR`, `afc`, `ulc_prime`, `avc_prime`, `ac_prime`, `mc_prime` |</t>
+          <t>| **S401-A** (the dataset's data column set) | output rows 0–20 (21 points, indexed by row, not year) | Shaikh, *Capitalism* (2016), Appendix 4.2 Table 4.2.4, per-worker-wage columns | money units per unit of output | Reconstructed CSV `SalvagedInputs/book_data/Reconstructed/Appendix_4_2_Table4.csv`, columns `XR`, `afc`, `ulc_prime`, `avc_prime`, `ac_prime`, `mc_prime` |</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>The reconstructed CSV resolves Phase 5 blocker CH4-B1 (verbatim transcription from book PDF pp. 772–781, validated to &lt;=0.02 rounding noise across all derived columns — see `Reconstructed/Appendix_4_2_README.md`).</t>
+          <t>The reconstructed table was transcribed verbatim from the source book (pp. 772–781) and matches the printed values to within 0.02 rounding noise across all derived columns (see `Reconstructed/Appendix_4_2_README.md`).</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S401 is `derived` (construction `formula`). Because the tabulated Appendix 4.2 values back-solve cleanly to the published formulas, the loader consumes the tabulated CSV directly and the processor writes the cost columns as-is (no re-derivation required for the book-period reproduction). The formula is documented here for traceability.</t>
+          <t>S401 is a `derived` series (built by formula). Because the tabulated Appendix 4.2 values back-solve cleanly to the published formulas, the data-loading step reads the tabulated table directly and the processing step writes the cost columns as-is (no re-derivation is required for the book-period reproduction). The formula is documented here for traceability.</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S401 emits one long-form row per XR observation, with `subseries_id` carrying the cost-component label.</t>
+          <t>The processing step emits one long-form row per output (XR) observation, with the subseries label carrying the cost-component name.</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>- **Book period**: not applicable (derived numerical illustration; the "axis" is cumulative output `XR`, not calendar year). Year-range fields in the registry are `[null, null]`; the loader stamps a synthetic ordinal index for downstream tooling.</t>
+          <t>- **Book period**: not applicable (derived numerical illustration; the "axis" is cumulative output `XR`, not calendar year). Year-range fields in the registry are `[null, null]`; the data-loading step stamps a synthetic ordinal index for downstream tooling.</t>
         </is>
       </c>
     </row>
@@ -4656,21 +4656,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1. **Not a time series.** The registry's `year_range` is `[null, null]`. We assign a synthetic ordinal `year = row_index` so the generic O06 chopped writer can persist the table. Downstream Phase 9 viz must plot against `XR` (not `year`).</t>
+          <t>1. **Not a time series.** The registry's `year_range` is `[null, null]`. We assign a synthetic ordinal `year = row_index` so the standard machine-readable (chopped) writer can persist the table. Downstream visualization must plot against output `XR` (not `year`).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2. **Appendix 4.2 published parameters are illustrative, not exactly reproducible.** Eq. (4.2.1) with the printed `a1=2, a2=1.2, a3=0.05` gives `xr(h=1)=3.15` whereas Table 4.2.1 prints `xr(h=1)=3.55` (+0.40 offset). Re-running the formula with back-solved `a1=2.40` recovers the tabulated values exactly. We do not re-derive in P02 — we consume the tabulated CSV directly. See `Reconstructed/Appendix_4_2_README.md` for full discussion.</t>
+          <t>2. **Appendix 4.2 published parameters are illustrative, not exactly reproducible.** Eq. (4.2.1) with the printed `a1=2, a2=1.2, a3=0.05` gives `xr(h=1)=3.15` whereas Table 4.2.1 prints `xr(h=1)=3.55` (+0.40 offset). Re-running the formula with back-solved `a1=2.40` recovers the tabulated values exactly. We do not re-derive in the processing step — we read the tabulated table directly. See `Reconstructed/Appendix_4_2_README.md` for full discussion.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3. **No CD/CD2 predecessor.** Fully fresh chapter (`CD2_to_RSCD_crosswalk.csv` has no Ch4 entries).</t>
+          <t>3. **No predecessor series.** This is a fully fresh chapter (no earlier-reconstruction entries for Chapter 4).</t>
         </is>
       </c>
     </row>
@@ -4697,355 +4697,348 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>- **Predecessor series**: none (first constructed in this dataset)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: none</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 4, p. 155 (Fig 4.16); Appendix 4.2 pp. 772–781</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 4, p. 155 (Fig 4.16); Appendix 4.2 pp. 772–781</t>
+          <t>- **Cross-series**: S402 (per-hour twin), S403 (profit derivation from S401 + S402)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>- **Cross-series**: S402 (per-hour twin), S403 (profit derivation from S401 + S402)</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: ±0.5% per cost-component row (the standard for a derived series).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>- **Tolerance**: ±0.5% per cost-component row (chapter playbook standard for `derived`).</t>
+          <t>- **Expected mean absolute error (MAE)**: 0 — the check round-trips the same table it reads.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>- **Expected MAE**: 0 — we round-trip the same CSV the validator reads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>- The V03 validator compares the processed parquet against `Appendix_4_2_Table4.csv` directly; any deviation &gt; 0.5% indicates pipeline corruption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4">
+          <t>- The validation step compares the processed data against `Appendix_4_2_Table4.csv` directly; any deviation greater than 0.5% indicates a pipeline error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4">
         <f>== EPR: S401_EPR.md ===</f>
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t># S401 — Extension Provenance Record</t>
+        </is>
+      </c>
+    </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t># S401 — Extension Provenance Record</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>**Series**: S401 — Average and Marginal Costs with Wage Paid per Worker (Fig 4.16)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>**Series**: S401 — Average and Marginal Costs with Wage Paid per Worker (Fig 4.16)</t>
+          <t>**Record type**: Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Construction classification**: `derived`</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>**Construction classification**: `derived`</t>
+          <t>**Extension method**: **not_applicable_theoretical**</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>**Extension method**: **not_applicable_theoretical**</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Author**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>## 1. Why this series is NOT extendable</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>## 1. Why this series is NOT extendable</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>S401 is a closed-form numerical illustration computed by Shaikh from Appendix 4.2 eq. (4.2.1) (a stylized quadratic productivity-per-hour curve) plus stylized prices (`pMK=100, pa=10, wN=100, p=7`). The horizontal axis is **cumulative daily output XR**, not calendar time. There is no calendar-year series to extend; there is no real-world data counterpart.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>S401 is a closed-form numerical illustration computed by Shaikh from Appendix 4.2 eq. (4.2.1) (a stylized quadratic productivity-per-hour curve) plus stylized prices (`pMK=100, pa=10, wN=100, p=7`). The horizontal axis is **cumulative daily output XR**, not calendar time. There is no calendar-year series to extend; there is no real-world data counterpart.</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Per the chapter playbook recipe for `derived`:</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Per the chapter playbook recipe for `derived`:</t>
+          <t>&gt; "Derived (e.g., Ch4 cost curves, S401-S407) — chopped CSV may be entirely book-truth values (no extension possible). Tolerance 0.5%."</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>&gt; "Derived (e.g., Ch4 cost curves, S401-S407) — chopped CSV may be entirely book-truth values (no extension possible). Tolerance 0.5%."</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>## 2. Construction classification</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>## 2. Construction classification</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>`derived` / `formula`. The Anu lazy-splice prohibition is vacuous here because there is no observed series on either side of the calendar boundary.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>`derived` / `formula`. The Anu lazy-splice prohibition is vacuous here because there is no observed series on either side of the calendar boundary.</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>## 3. Method</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>## 3. Method</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Not applicable.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>## 4. Component re-fetching</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Not applicable.</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>## 4. Component re-fetching</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-    </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Not applicable.</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>## 5. Proxies</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>## 5. Proxies</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>**None.** No substitution required because no extension is attempted.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>**None.** No substitution required because no extension is attempted.</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>## 6. Synthetic data</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>## 6. Synthetic data</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>**None.** The book values are themselves the only "data" in question; we ingest them verbatim from the reconstructed CSV. We do not back-solve eq. (4.2.1) at runtime — the CSV is the canonical source.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>**None.** The book values are themselves the only "data" in question; we ingest them verbatim from the reconstructed CSV. We do not back-solve eq. (4.2.1) at runtime — the CSV is the canonical source.</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>## 7. Failure modes &amp; graceful degradation</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>## 7. Failure modes &amp; graceful degradation</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Action |</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>| Reconstructed CSV missing | The data-loading step checks that `Appendix_4_2_Table4.csv` exists | The data-loading step returns FAIL with the explicit path |</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>| Reconstructed CSV missing | L01 checks `Appendix_4_2_Table4.csv` exists | Loader returns FAIL with explicit path |</t>
+          <t>| CSV schema drift (column rename) | The data-loading step's explicit column list | The data-loading step returns FAIL with a missing-column report |</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>| CSV schema drift (column rename) | L01 explicit column list | Loader returns FAIL with missing-column report |</t>
+          <t>| Empty XR=0 row mis-parsed | The data-loading step preserves nulls in non-`afc` columns | The processing step passes through; the validation step treats nulls as not-compared |</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>| Empty XR=0 row mis-parsed | L01 preserves nulls in non-`afc` columns | Processor passes through; validator treats nulls as not-compared |</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>## 8. Predecessor divergence</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>## 8. CD2 divergence</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>**Not applicable** — no earlier reconstruction of this project (internally called CD/CD2) contained any Chapter 4 series.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>**Not applicable** — no CD/CD2 predecessor for any Ch4 series.</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>## 9. Forward roadmap</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>## 9. Forward roadmap</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>A possible Phase 9 visualization would re-derive the cost curves on a finer XR grid by re-implementing eq. (4.2.1) directly (with the back-solved `a1=2.40`); that re-derivation would be a viz convenience, **not** an extension of S401, and is out of scope for Phases 5–8.</t>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>A possible later chapter-level visualization would re-derive the cost curves on a finer XR grid by re-implementing eq. (4.2.1) directly (with the back-solved `a1=2.40`); that re-derivation would be a visualization convenience, **not** an extension of S401, and is out of scope for the present data-construction work.</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5453,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5569,7 +5562,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:03:23.168804+00:00</t>
+          <t>2026-07-02T06:22:29.982345+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S401_extenbook.xlsx
+++ b/extenbooks/S401_extenbook.xlsx
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:29.982345+00:00</t>
+          <t>2026-07-11T03:44:24.772827+00:00</t>
         </is>
       </c>
     </row>
@@ -5577,11 +5577,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5604,6 +5604,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_4_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable multi-trace cost curve (Shaikh Fig 4.16): six cost components (afc, ulc', avc', ac', tc', mc') vs cumulative daily output XR across a three-shift day, paying wages per worker. 6 subseries x 21 points = 126 rows (4 nulls are the mathematically-undefined ac' at XR=0, expected). Renders as overlaid x-y cost curves (x = cumulative output XR, carried in the 'year' index column 0-9, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag is STALE: L01_S401/P02_S401 exist and replicate.py --series S401 builds the chopped (PASS, 126 rows). Data is a VERBATIM transcription of Appendix Table 4.2.4 (book pp.772-781), validated to &lt;=0.02 rounding noise. KB note: the chapter-4 main text is not HDARP-extracted, BUT Appendix 4.2 (the actual source of this series) IS present in ch18_appendices.md, so a 'From the book' quote anchored to ch18/Appendix 4.2 is verifiable and is included in the explainer.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S401_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S401_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Derived numerical illustration of Fig 4.16 (per-worker wage cost curves). XR-axis, not calendar-time. Phase 5 blocker CH4-B1 resolved 2026-05-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>money_units_per_unit_output_illustrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
